--- a/fetching-taxes/auto-fetcher/local_taxes.xlsx
+++ b/fetching-taxes/auto-fetcher/local_taxes.xlsx
@@ -1,26 +1,17 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
   <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\YXQia\OneDrive\Documents\AI Projects\smart-cd-ai\fetching-taxes\locally\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3BF49946-2587-4287-9AA2-03788411C362}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
-  <bookViews>
-    <workbookView xWindow="-105" yWindow="0" windowWidth="19530" windowHeight="20985" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
-  </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet state="visible" name="Sheet1" sheetId="1" r:id="rId5"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <definedNames/>
+  <calcPr/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="70" uniqueCount="37">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="74" uniqueCount="37">
   <si>
     <t>state</t>
   </si>
@@ -136,63 +127,75 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <fonts count="2">
     <font>
-      <sz val="10"/>
+      <sz val="10.0"/>
       <color rgb="FF000000"/>
       <name val="Arial"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="10"/>
       <color theme="1"/>
       <name val="Arial"/>
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
-      <patternFill patternType="gray125"/>
+      <patternFill patternType="lightGray"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor rgb="FFFFFF00"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor rgb="FFFFFFFF"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="1">
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
+    <border/>
   </borders>
   <cellStyleXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="2">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+  <cellXfs count="4">
+    <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment readingOrder="0"/>
+    </xf>
+    <xf borderId="0" fillId="2" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFill="1" applyFont="1">
+      <alignment readingOrder="0"/>
+    </xf>
+    <xf borderId="0" fillId="3" fontId="1" numFmtId="0" xfId="0" applyFill="1" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle xfId="0" name="Normal" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
-  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
-  </extLst>
 </styleSheet>
 </file>
 
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<x18tc:personList xmlns:x18tc="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments"/>
+</file>
+
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Sheets">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheets">
   <a:themeElements>
     <a:clrScheme name="Sheets">
       <a:dk1>
@@ -382,23 +385,20 @@
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
-  <a:objectDefaults/>
-  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <dimension ref="A1:D37"/>
-  <sheetFormatPr defaultColWidth="12.5703125" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.75"/>
   <cols>
-    <col min="4" max="4" width="19.28515625" customWidth="1"/>
+    <col customWidth="1" min="4" max="4" width="19.25"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="1">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -412,7 +412,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="2">
       <c r="A2" s="1" t="s">
         <v>4</v>
       </c>
@@ -423,7 +423,7 @@
         <v>2.75</v>
       </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="3">
       <c r="A3" s="1" t="s">
         <v>4</v>
       </c>
@@ -434,7 +434,7 @@
         <v>2.75</v>
       </c>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="4">
       <c r="A4" s="1" t="s">
         <v>4</v>
       </c>
@@ -442,10 +442,10 @@
         <v>7</v>
       </c>
       <c r="D4" s="1">
-        <v>2.4700000000000002</v>
-      </c>
-    </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.2">
+        <v>2.47</v>
+      </c>
+    </row>
+    <row r="5">
       <c r="A5" s="1" t="s">
         <v>4</v>
       </c>
@@ -456,7 +456,7 @@
         <v>2.35</v>
       </c>
     </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="6">
       <c r="A6" s="1" t="s">
         <v>4</v>
       </c>
@@ -467,7 +467,7 @@
         <v>2.35</v>
       </c>
     </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="7">
       <c r="A7" s="1" t="s">
         <v>4</v>
       </c>
@@ -478,7 +478,7 @@
         <v>1.7</v>
       </c>
     </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="8">
       <c r="A8" s="1" t="s">
         <v>4</v>
       </c>
@@ -489,7 +489,7 @@
         <v>2.02</v>
       </c>
     </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="9">
       <c r="A9" s="1" t="s">
         <v>4</v>
       </c>
@@ -497,10 +497,10 @@
         <v>12</v>
       </c>
       <c r="D9" s="1">
-        <v>1.1000000000000001</v>
-      </c>
-    </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.2">
+        <v>1.1</v>
+      </c>
+    </row>
+    <row r="10">
       <c r="A10" s="1" t="s">
         <v>4</v>
       </c>
@@ -511,7 +511,7 @@
         <v>1.59</v>
       </c>
     </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="11">
       <c r="A11" s="1" t="s">
         <v>4</v>
       </c>
@@ -522,7 +522,7 @@
         <v>2.75</v>
       </c>
     </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="12">
       <c r="A12" s="1" t="s">
         <v>4</v>
       </c>
@@ -533,7 +533,7 @@
         <v>2.75</v>
       </c>
     </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="13">
       <c r="A13" s="1" t="s">
         <v>4</v>
       </c>
@@ -544,7 +544,7 @@
         <v>1.75</v>
       </c>
     </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="14">
       <c r="A14" s="1" t="s">
         <v>4</v>
       </c>
@@ -555,7 +555,7 @@
         <v>1.2</v>
       </c>
     </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="15">
       <c r="A15" s="1" t="s">
         <v>4</v>
       </c>
@@ -566,7 +566,7 @@
         <v>1.5</v>
       </c>
     </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="16">
       <c r="A16" s="1" t="s">
         <v>4</v>
       </c>
@@ -574,10 +574,10 @@
         <v>17</v>
       </c>
       <c r="D16" s="1">
-        <v>2.0299999999999998</v>
-      </c>
-    </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.2">
+        <v>2.03</v>
+      </c>
+    </row>
+    <row r="17">
       <c r="A17" s="1" t="s">
         <v>4</v>
       </c>
@@ -588,18 +588,18 @@
         <v>2.95</v>
       </c>
     </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="18">
       <c r="A18" s="1" t="s">
         <v>4</v>
       </c>
       <c r="B18" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="D18" s="1">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="D18" s="2">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="20">
       <c r="A20" s="1" t="s">
         <v>20</v>
       </c>
@@ -610,7 +610,7 @@
         <v>3.2</v>
       </c>
     </row>
-    <row r="21" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="21">
       <c r="A21" s="1" t="s">
         <v>20</v>
       </c>
@@ -621,7 +621,7 @@
         <v>3.2</v>
       </c>
     </row>
-    <row r="22" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="22">
       <c r="A22" s="1" t="s">
         <v>20</v>
       </c>
@@ -632,7 +632,7 @@
         <v>3.2</v>
       </c>
     </row>
-    <row r="23" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="23">
       <c r="A23" s="1" t="s">
         <v>20</v>
       </c>
@@ -640,10 +640,10 @@
         <v>24</v>
       </c>
       <c r="D23" s="1">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="24" spans="1:4" x14ac:dyDescent="0.2">
+        <v>3.0</v>
+      </c>
+    </row>
+    <row r="24">
       <c r="A24" s="1" t="s">
         <v>20</v>
       </c>
@@ -654,7 +654,7 @@
         <v>3.2</v>
       </c>
     </row>
-    <row r="25" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="25">
       <c r="A25" s="1" t="s">
         <v>20</v>
       </c>
@@ -662,10 +662,10 @@
         <v>25</v>
       </c>
       <c r="D25" s="1">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="26" spans="1:4" x14ac:dyDescent="0.2">
+        <v>3.0</v>
+      </c>
+    </row>
+    <row r="26">
       <c r="A26" s="1" t="s">
         <v>20</v>
       </c>
@@ -676,7 +676,7 @@
         <v>2.4</v>
       </c>
     </row>
-    <row r="27" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="27">
       <c r="A27" s="1" t="s">
         <v>20</v>
       </c>
@@ -687,18 +687,18 @@
         <v>2.25</v>
       </c>
     </row>
-    <row r="28" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="28">
       <c r="A28" s="1" t="s">
         <v>20</v>
       </c>
       <c r="B28" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="D28" s="1">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="30" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="D28" s="2">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="30">
       <c r="A30" s="1" t="s">
         <v>28</v>
       </c>
@@ -706,10 +706,10 @@
         <v>29</v>
       </c>
       <c r="D30" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="31" spans="1:4" x14ac:dyDescent="0.2">
+        <v>1.0</v>
+      </c>
+    </row>
+    <row r="31">
       <c r="A31" s="1" t="s">
         <v>28</v>
       </c>
@@ -720,7 +720,7 @@
         <v>3.5</v>
       </c>
     </row>
-    <row r="32" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="32">
       <c r="A32" s="1" t="s">
         <v>28</v>
       </c>
@@ -731,7 +731,7 @@
         <v>3.5</v>
       </c>
     </row>
-    <row r="33" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="33">
       <c r="A33" s="1" t="s">
         <v>28</v>
       </c>
@@ -742,7 +742,7 @@
         <v>3.5</v>
       </c>
     </row>
-    <row r="34" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="34">
       <c r="A34" s="1" t="s">
         <v>28</v>
       </c>
@@ -753,7 +753,7 @@
         <v>3.5</v>
       </c>
     </row>
-    <row r="35" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="35">
       <c r="A35" s="1" t="s">
         <v>28</v>
       </c>
@@ -764,18 +764,46 @@
         <v>3.5</v>
       </c>
     </row>
-    <row r="37" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A37" s="1" t="s">
+    <row r="36">
+      <c r="A36" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="C36" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="D36" s="2">
+        <v>0.0</v>
+      </c>
+      <c r="F36" s="3"/>
+    </row>
+    <row r="37">
+      <c r="A37" s="1"/>
+      <c r="C37" s="1"/>
+      <c r="D37" s="1"/>
+    </row>
+    <row r="38">
+      <c r="A38" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="C37" s="1" t="s">
+      <c r="C38" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="D37" s="1">
+      <c r="D38" s="1">
         <v>2.4</v>
       </c>
     </row>
+    <row r="39">
+      <c r="A39" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="C39" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="D39" s="2">
+        <v>0.0</v>
+      </c>
+    </row>
   </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
 </worksheet>
 </file>